--- a/Data/Hires/testDataNetherland1.xlsx
+++ b/Data/Hires/testDataNetherland1.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEB7C9E-C9BF-410E-AC20-514EC5C73C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,19 +208,25 @@
     <t>NameOnAccount</t>
   </si>
   <si>
+    <t>10699614</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>701 Recruitment (Vulam Syhohu (8701689))</t>
   </si>
   <si>
     <t>Mevr</t>
   </si>
   <si>
-    <t>Aubrey</t>
+    <t>Aubree</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Waters</t>
+    <t>Davis</t>
   </si>
   <si>
     <t>071 025 8087</t>
@@ -354,19 +346,16 @@
     <t>40</t>
   </si>
   <si>
-    <t>10699525</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>10699616</t>
   </si>
   <si>
     <t>701 Store Management (Vulam Syhohu (8701689))</t>
   </si>
   <si>
-    <t>Federico</t>
-  </si>
-  <si>
-    <t>Schroeder</t>
+    <t>Rhiannon</t>
+  </si>
+  <si>
+    <t>Schamberger</t>
   </si>
   <si>
     <t>Full-time( FT. )</t>
@@ -375,7 +364,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 36795961</t>
+    <t>Auto 44499944</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -393,79 +382,79 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF040C28"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FF040C28"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF4A4A4A"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -477,13 +466,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,55 +503,33 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -573,9 +540,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -588,35 +553,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
@@ -1021,9 +972,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BN3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="58.1796875" customWidth="1"/>
     <col min="4" max="4" width="59" customWidth="1"/>
@@ -1066,7 +1017,7 @@
     <col min="66" max="66" width="39.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,328 +1217,328 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:66" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13">
-        <v>10699524</v>
+    <row r="2" ht="87.5" customHeight="1" spans="2:66" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45786</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="P2" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="S2" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="U2" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" s="18" t="s">
-        <v>71</v>
-      </c>
       <c r="W2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="X2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Z2" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="23">
-        <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45779</v>
+        <f t="shared" ref="AB2:AB3" si="1">AG2</f>
+        <v>45786</v>
       </c>
       <c r="AC2" s="28">
-        <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45779</v>
+        <f t="shared" ref="AC2:AC3" si="2">AG2</f>
+        <v>45786</v>
       </c>
       <c r="AD2" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE2" s="30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF2" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="31">
-        <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45779</v>
+        <f t="shared" ref="AG2:AG3" si="3">L2</f>
+        <v>45786</v>
       </c>
       <c r="AH2" s="23">
         <v>44986</v>
       </c>
       <c r="AI2" s="18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AJ2" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL2" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AM2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AN2" s="20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP2" s="34">
         <v>25</v>
       </c>
       <c r="AQ2" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AR2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS2" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX2" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY2" s="37">
+        <v>100000030</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA2" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG2" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="BH2" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI2" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ2" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK2" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="BL2" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BN2" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" customHeight="1" spans="2:66" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="19">
+        <f t="shared" si="0"/>
+        <v>45786</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" t="s">
+        <v>75</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA3" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB3" s="23">
+        <f t="shared" si="1"/>
+        <v>45786</v>
+      </c>
+      <c r="AC3" s="28">
+        <f t="shared" si="2"/>
+        <v>45786</v>
+      </c>
+      <c r="AD3" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE3" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF3" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG3" s="31">
+        <f t="shared" si="3"/>
+        <v>45786</v>
+      </c>
+      <c r="AH3" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI3" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="AJ3" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK3" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL3" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM3" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN3" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="AS2" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT2" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU2" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW2" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="AX2" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY2" s="37">
-        <v>100000027</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA2" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB2" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="BE2" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BG2" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="BH2" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI2" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="BJ2" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK2" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL2" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN2" s="39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="R3" t="s">
-        <v>73</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="U3" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" t="s">
-        <v>79</v>
-      </c>
-      <c r="X3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y3" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z3" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA3" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB3" s="23">
-        <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
-      </c>
-      <c r="AC3" s="28">
-        <f t="shared" ca="1" si="2"/>
-        <v>45779</v>
-      </c>
-      <c r="AD3" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE3" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF3" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG3" s="31">
-        <f t="shared" ca="1" si="3"/>
-        <v>45779</v>
-      </c>
-      <c r="AH3" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI3" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="AJ3" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK3" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL3" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="AM3" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN3" s="20" t="s">
-        <v>91</v>
       </c>
       <c r="AO3" s="20" t="s">
         <v>56</v>
@@ -1596,92 +1547,104 @@
         <v>40</v>
       </c>
       <c r="AQ3" s="20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AR3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AS3" s="35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AT3" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AU3" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AV3" s="37">
         <v>251</v>
       </c>
       <c r="AW3" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AX3" s="36" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AY3" s="37">
-        <v>100000028</v>
+        <v>100000031</v>
       </c>
       <c r="AZ3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BA3" s="38">
         <v>35591</v>
       </c>
       <c r="BB3" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BC3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BD3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BE3" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BF3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BG3" s="20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BH3" s="36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BI3" s="36" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BJ3" s="36" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BK3" s="36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BL3" s="40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BM3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BN3" s="41" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2 V2:V3 S2:S3 K2:K3 BK2:BK3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK3">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+      <formula1>INDIRECT(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/testDataNetherland1.xlsx
+++ b/Data/Hires/testDataNetherland1.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFDEBED-F46B-4B1A-B9B8-DA1614F5DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,253 +222,247 @@
     <t>NameOnAccount</t>
   </si>
   <si>
-    <t>10699614</t>
+    <t>701 Recruitment (Vulam Syhohu (8701689))</t>
+  </si>
+  <si>
+    <t>Mevr</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Sanford</t>
+  </si>
+  <si>
+    <t>071 025 8087</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>North Brabant</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>1111AZ</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>automation@qe.com</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>0 – Niet verzekerd</t>
+  </si>
+  <si>
+    <t>Undefined contract end date (Undetermined)</t>
+  </si>
+  <si>
+    <t>Part-time( PT )</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Netherlands Retail Assistant</t>
+  </si>
+  <si>
+    <t>Retail Assistant (23+)</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Retail Assistant</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>701 Hoofddorp</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>5 Days (Netherlands)</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t>94 Retail Operative</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Personal Number (Burgerservicenr)</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>06/10/1997</t>
+  </si>
+  <si>
+    <t>Citizen (Netherlands)</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>BON</t>
+  </si>
+  <si>
+    <t>BOFIIE2D</t>
+  </si>
+  <si>
+    <t>NL02ABNA0123456789</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>NL 4-Weekly</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>701 Store Management (Vulam Syhohu (8701689))</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Emmerich</t>
+  </si>
+  <si>
+    <t>Full-time( FT. )</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Auto 71847621</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>92 Retail Management</t>
+  </si>
+  <si>
+    <t>NL Management</t>
   </si>
   <si>
     <t>Passed</t>
-  </si>
-  <si>
-    <t>701 Recruitment (Vulam Syhohu (8701689))</t>
-  </si>
-  <si>
-    <t>Mevr</t>
-  </si>
-  <si>
-    <t>Aubree</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>071 025 8087</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>North Brabant</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>1111AZ</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>automation@qe.com</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>0 – Niet verzekerd</t>
-  </si>
-  <si>
-    <t>Undefined contract end date (Undetermined)</t>
-  </si>
-  <si>
-    <t>Part-time( PT )</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Netherlands Retail Assistant</t>
-  </si>
-  <si>
-    <t>Retail Assistant (23+)</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Retail Assistant</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>701 Hoofddorp</t>
-  </si>
-  <si>
-    <t>Hourly</t>
-  </si>
-  <si>
-    <t>5 Days (Netherlands)</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t>94 Retail Operative</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Personal Number (Burgerservicenr)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>06/10/1997</t>
-  </si>
-  <si>
-    <t>Citizen (Netherlands)</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>BON</t>
-  </si>
-  <si>
-    <t>BOFIIE2D</t>
-  </si>
-  <si>
-    <t>NL02ABNA0123456789</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>NL 4-Weekly</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>10699616</t>
-  </si>
-  <si>
-    <t>701 Store Management (Vulam Syhohu (8701689))</t>
-  </si>
-  <si>
-    <t>Rhiannon</t>
-  </si>
-  <si>
-    <t>Schamberger</t>
-  </si>
-  <si>
-    <t>Full-time( FT. )</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Auto 44499944</t>
-  </si>
-  <si>
-    <t>Store Manager</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>92 Retail Management</t>
-  </si>
-  <si>
-    <t>NL Management</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF040C28"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -466,13 +474,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,7 +492,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -503,33 +511,55 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -540,7 +570,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -553,21 +585,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -972,9 +1018,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.1796875" customWidth="1"/>
     <col min="4" max="4" width="59" customWidth="1"/>
@@ -1017,7 +1063,7 @@
     <col min="66" max="66" width="39.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:66" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1217,328 +1263,328 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="87.5" customHeight="1" spans="2:66" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="1:66" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="13">
+        <v>10699772</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="K2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="L2" s="19">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45796</v>
+      </c>
+      <c r="M2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="N2" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45786</v>
-      </c>
-      <c r="M2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="Q2" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="R2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="U2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="R2" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="T2" s="23" t="s">
+      <c r="V2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="X2" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="Y2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="AA2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="26" t="s">
+      <c r="AB2" s="23">
+        <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
+        <v>45796</v>
+      </c>
+      <c r="AC2" s="28">
+        <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
+        <v>45796</v>
+      </c>
+      <c r="AD2" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AE2" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="23">
-        <f t="shared" ref="AB2:AB3" si="1">AG2</f>
-        <v>45786</v>
-      </c>
-      <c r="AC2" s="28">
-        <f t="shared" ref="AC2:AC3" si="2">AG2</f>
-        <v>45786</v>
-      </c>
-      <c r="AD2" s="29" t="s">
+      <c r="AF2" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF2" s="30" t="s">
-        <v>88</v>
-      </c>
       <c r="AG2" s="31">
-        <f t="shared" ref="AG2:AG3" si="3">L2</f>
-        <v>45786</v>
+        <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
+        <v>45796</v>
       </c>
       <c r="AH2" s="23">
         <v>44986</v>
       </c>
       <c r="AI2" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK2" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL2" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="AJ2" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK2" s="32" t="s">
+      <c r="AM2" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="AL2" s="33" t="s">
+      <c r="AN2" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AM2" s="32" t="s">
+      <c r="AO2" s="20" t="s">
         <v>92</v>
-      </c>
-      <c r="AN2" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="AO2" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="AP2" s="34">
         <v>25</v>
       </c>
       <c r="AQ2" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AR2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS2" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT2" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU2" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="AS2" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT2" s="18" t="s">
+      <c r="AV2" t="s">
         <v>96</v>
       </c>
-      <c r="AU2" s="18" t="s">
+      <c r="AW2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX2" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" s="37">
+        <v>100000038</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>98</v>
       </c>
-      <c r="AW2" s="20" t="s">
+      <c r="BA2" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BG2" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH2" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="BI2" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="BJ2" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK2" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL2" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN2" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="13">
+        <v>10699774</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="19">
+        <f t="shared" ca="1" si="0"/>
+        <v>45796</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="AX2" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="AY2" s="37">
-        <v>100000030</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA2" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="BB2" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="BC2" t="s">
+      <c r="P3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="BD2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE2" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BG2" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="BH2" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="BI2" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="BJ2" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="BK2" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="BL2" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>109</v>
-      </c>
-      <c r="BN2" s="39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="2:66" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="Q3" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="T3" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="U3" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="V3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>79</v>
+      </c>
+      <c r="X3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="AA3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB3" s="23">
+        <f t="shared" ca="1" si="1"/>
+        <v>45796</v>
+      </c>
+      <c r="AC3" s="28">
+        <f t="shared" ca="1" si="2"/>
+        <v>45796</v>
+      </c>
+      <c r="AD3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF3" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG3" s="31">
+        <f t="shared" ca="1" si="3"/>
+        <v>45796</v>
+      </c>
+      <c r="AH3" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="16" t="s">
+      <c r="AJ3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="19">
-        <f t="shared" si="0"/>
-        <v>45786</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="N3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q3" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="R3" t="s">
-        <v>75</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y3" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z3" s="25" t="s">
+      <c r="AK3" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL3" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="AA3" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3" s="23">
-        <f t="shared" si="1"/>
-        <v>45786</v>
-      </c>
-      <c r="AC3" s="28">
-        <f t="shared" si="2"/>
-        <v>45786</v>
-      </c>
-      <c r="AD3" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF3" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG3" s="31">
-        <f t="shared" si="3"/>
-        <v>45786</v>
-      </c>
-      <c r="AH3" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI3" s="18" t="s">
+      <c r="AM3" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="AJ3" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK3" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL3" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" s="32" t="s">
-        <v>118</v>
-      </c>
       <c r="AN3" s="20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AO3" s="20" t="s">
         <v>56</v>
@@ -1547,104 +1593,92 @@
         <v>40</v>
       </c>
       <c r="AQ3" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AR3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AS3" s="35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AT3" s="18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AU3" s="18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AV3" s="37">
         <v>251</v>
       </c>
       <c r="AW3" s="20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AX3" s="36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AY3" s="37">
-        <v>100000031</v>
+        <v>100000039</v>
       </c>
       <c r="AZ3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="BA3" s="38">
         <v>35591</v>
       </c>
       <c r="BB3" s="20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BC3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BD3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BE3" s="20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="BF3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BG3" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH3" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="BG3" s="20" t="s">
+      <c r="BI3" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="BH3" s="36" t="s">
+      <c r="BJ3" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="36" t="s">
+      <c r="BK3" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="BJ3" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="BK3" s="36" t="s">
+      <c r="BL3" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="s">
         <v>107</v>
       </c>
-      <c r="BL3" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>109</v>
-      </c>
       <c r="BN3" s="41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK3">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
-      <formula1>INDIRECT(#REF!)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2 V2:V3 S2:S3 K2:K3 BK2:BK3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
-    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/testDataNetherland1.xlsx
+++ b/Data/Hires/testDataNetherland1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFDEBED-F46B-4B1A-B9B8-DA1614F5DC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA8F610-E24E-4066-9251-5F91DD648286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1019,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.1796875" customWidth="1"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>72</v>
@@ -1345,11 +1345,11 @@
       </c>
       <c r="AB2" s="23">
         <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AC2" s="28">
         <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AD2" s="29" t="s">
         <v>84</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AG2" s="31">
         <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AH2" s="23">
         <v>44986</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L3" s="19">
         <f t="shared" ca="1" si="0"/>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="M3" s="20" t="s">
         <v>72</v>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="AB3" s="23">
         <f t="shared" ca="1" si="1"/>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AD3" s="29" t="s">
         <v>84</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG3" s="31">
         <f t="shared" ca="1" si="3"/>
-        <v>45796</v>
+        <v>45830</v>
       </c>
       <c r="AH3" s="26" t="s">
         <v>84</v>
@@ -1664,6 +1664,10 @@
       <c r="BN3" s="41" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="7" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Data/Hires/testDataNetherland1.xlsx
+++ b/Data/Hires/testDataNetherland1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35593B9F-8C9F-4E90-9569-F7F4E936D8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD706D72-1E3E-432B-85CC-382640ACF536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="130">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,7 +222,7 @@
     <t>NameOnAccount</t>
   </si>
   <si>
-    <t>10700250</t>
+    <t>10700438</t>
   </si>
   <si>
     <t>Passed</t>
@@ -234,13 +234,13 @@
     <t>Mevr</t>
   </si>
   <si>
-    <t>Emie</t>
+    <t>Winnifred</t>
   </si>
   <si>
     <t>Test</t>
   </si>
   <si>
-    <t>Bogisich</t>
+    <t>Fadel-Schoen</t>
   </si>
   <si>
     <t>071 025 8087</t>
@@ -333,9 +333,6 @@
     <t>Male</t>
   </si>
   <si>
-    <t>06/10/1997</t>
-  </si>
-  <si>
     <t>Citizen (Netherlands)</t>
   </si>
   <si>
@@ -357,16 +354,13 @@
     <t>NL 4-Weekly</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>701 Store Management (Vulam Syhohu (8701689))</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>Mueller</t>
+    <t>Arlene</t>
+  </si>
+  <si>
+    <t>Christiansen</t>
   </si>
   <si>
     <t>Full-time( FT. )</t>
@@ -375,7 +369,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 49569171</t>
+    <t>Auto 17264735</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -388,6 +382,42 @@
   </si>
   <si>
     <t>NL Management</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>Haleigh</t>
+  </si>
+  <si>
+    <t>Ritchie</t>
+  </si>
+  <si>
+    <t>Auto 51023958</t>
+  </si>
+  <si>
+    <t>Jasen</t>
+  </si>
+  <si>
+    <t>Dare</t>
+  </si>
+  <si>
+    <t>Jannie</t>
+  </si>
+  <si>
+    <t>Kuhic</t>
+  </si>
+  <si>
+    <t>Auto 98490906</t>
+  </si>
+  <si>
+    <t>Brianne</t>
+  </si>
+  <si>
+    <t>Tillman</t>
   </si>
 </sst>
 </file>
@@ -495,8 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -627,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -741,6 +770,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1022,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="58.1796875" customWidth="1"/>
@@ -1298,8 +1330,8 @@
         <v>73</v>
       </c>
       <c r="L2" s="18">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <f t="shared" ref="L2:L8" ca="1" si="0">TODAY()-31</f>
+        <v>45842</v>
       </c>
       <c r="M2" s="19" t="s">
         <v>74</v>
@@ -1348,11 +1380,11 @@
       </c>
       <c r="AB2" s="22">
         <f t="shared" ref="AB2:AB3" ca="1" si="1">AG2</f>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AC2" s="27">
         <f t="shared" ref="AC2:AC3" ca="1" si="2">AG2</f>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AD2" s="28" t="s">
         <v>86</v>
@@ -1365,7 +1397,7 @@
       </c>
       <c r="AG2" s="30">
         <f t="shared" ref="AG2:AG3" ca="1" si="3">L2</f>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AH2" s="22">
         <v>44986</v>
@@ -1419,13 +1451,13 @@
         <v>99</v>
       </c>
       <c r="AY2" s="36">
-        <v>100000059</v>
+        <v>100000083</v>
       </c>
       <c r="AZ2" t="s">
         <v>100</v>
       </c>
-      <c r="BA2" s="37" t="s">
-        <v>101</v>
+      <c r="BA2" s="37">
+        <v>35709</v>
       </c>
       <c r="BB2" s="19" t="s">
         <v>74</v>
@@ -1440,28 +1472,28 @@
         <v>74</v>
       </c>
       <c r="BF2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG2" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" s="19" t="s">
+      <c r="BH2" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="BH2" s="35" t="s">
+      <c r="BI2" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="BI2" s="35" t="s">
+      <c r="BJ2" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="BJ2" s="35" t="s">
+      <c r="BK2" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="BK2" s="35" t="s">
+      <c r="BL2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="BL2" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>109</v>
+      <c r="BM2">
+        <v>38</v>
       </c>
       <c r="BN2" s="38" t="s">
         <v>69</v>
@@ -1469,25 +1501,25 @@
     </row>
     <row r="3" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="13">
-        <v>10700252</v>
+        <v>10700439</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>65</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>67</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>69</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>71</v>
@@ -1500,7 +1532,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="M3" s="19" t="s">
         <v>74</v>
@@ -1542,18 +1574,18 @@
         <v>83</v>
       </c>
       <c r="Z3" s="24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AA3" s="26" t="s">
         <v>85</v>
       </c>
       <c r="AB3" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AC3" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AD3" s="28" t="s">
         <v>86</v>
@@ -1566,25 +1598,25 @@
       </c>
       <c r="AG3" s="30">
         <f t="shared" ca="1" si="3"/>
-        <v>45822</v>
+        <v>45842</v>
       </c>
       <c r="AH3" s="25" t="s">
         <v>86</v>
       </c>
       <c r="AI3" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AJ3" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK3" s="31" t="s">
         <v>90</v>
       </c>
       <c r="AL3" s="32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AM3" s="31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AN3" s="19" t="s">
         <v>93</v>
@@ -1608,7 +1640,7 @@
         <v>96</v>
       </c>
       <c r="AU3" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AV3" s="36">
         <v>251</v>
@@ -1620,7 +1652,7 @@
         <v>99</v>
       </c>
       <c r="AY3" s="36">
-        <v>100000060</v>
+        <v>100000084</v>
       </c>
       <c r="AZ3" t="s">
         <v>100</v>
@@ -1641,45 +1673,1055 @@
         <v>74</v>
       </c>
       <c r="BF3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BH3" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="BH3" s="35" t="s">
+      <c r="BI3" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="BI3" s="35" t="s">
+      <c r="BJ3" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="BJ3" s="35" t="s">
+      <c r="BK3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="BK3" s="35" t="s">
+      <c r="BL3" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM3">
+        <v>40</v>
+      </c>
+      <c r="BN3" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="41">
+        <v>10700440</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" t="s">
+        <v>75</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T4" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" t="s">
+        <v>81</v>
+      </c>
+      <c r="X4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z4" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA4" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB4" s="22">
+        <f t="shared" ref="AB4:AB8" ca="1" si="4">AG4</f>
+        <v>45842</v>
+      </c>
+      <c r="AC4" s="27">
+        <f t="shared" ref="AC4:AC8" ca="1" si="5">AG4</f>
+        <v>45842</v>
+      </c>
+      <c r="AD4" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE4" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF4" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG4" s="30">
+        <f t="shared" ref="AG4:AG8" ca="1" si="6">L4</f>
+        <v>45842</v>
+      </c>
+      <c r="AH4" s="22">
+        <v>44986</v>
+      </c>
+      <c r="AI4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ4" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK4" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL4" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM4" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO4" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP4" s="33">
+        <v>25</v>
+      </c>
+      <c r="AQ4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS4" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU4" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW4" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX4" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY4" s="36">
+        <v>100000085</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA4" s="37">
+        <v>35709</v>
+      </c>
+      <c r="BB4" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE4" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH4" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI4" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ4" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK4" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL4" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="BL3" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>109</v>
-      </c>
-      <c r="BN3" s="40" t="s">
+      <c r="BM4">
+        <v>38</v>
+      </c>
+      <c r="BN4" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="41">
+        <v>10700441</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>75</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W5" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z5" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA5" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB5" s="22">
+        <f t="shared" ca="1" si="4"/>
+        <v>45842</v>
+      </c>
+      <c r="AC5" s="27">
+        <f t="shared" ca="1" si="5"/>
+        <v>45842</v>
+      </c>
+      <c r="AD5" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE5" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF5" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG5" s="30">
+        <f t="shared" ca="1" si="6"/>
+        <v>45842</v>
+      </c>
+      <c r="AH5" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI5" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ5" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK5" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL5" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM5" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="AN5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO5" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP5" s="33">
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS5" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU5" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV5" s="36">
+        <v>251</v>
+      </c>
+      <c r="AW5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX5" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY5" s="36">
+        <v>100000086</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA5" s="37">
+        <v>35591</v>
+      </c>
+      <c r="BB5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE5" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG5" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH5" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI5" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ5" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK5" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL5" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM5">
+        <v>40</v>
+      </c>
+      <c r="BN5" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>10700442</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T6" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" t="s">
+        <v>81</v>
+      </c>
+      <c r="X6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z6" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA6" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB6" s="22">
+        <f t="shared" ca="1" si="4"/>
+        <v>45842</v>
+      </c>
+      <c r="AC6" s="27">
+        <f t="shared" ca="1" si="5"/>
+        <v>45842</v>
+      </c>
+      <c r="AD6" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE6" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF6" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG6" s="30">
+        <f t="shared" ca="1" si="6"/>
+        <v>45842</v>
+      </c>
+      <c r="AH6" s="22">
+        <v>44986</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ6" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK6" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL6" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM6" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP6" s="33">
+        <v>25</v>
+      </c>
+      <c r="AQ6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU6" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW6" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX6" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY6" s="36">
+        <v>100000087</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA6" s="37">
+        <v>35709</v>
+      </c>
+      <c r="BB6" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE6" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG6" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH6" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI6" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ6" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK6" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL6" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM6">
+        <v>38</v>
+      </c>
+      <c r="BN6" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="41">
+        <v>10700443</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N7" t="s">
+        <v>75</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" t="s">
+        <v>75</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T7" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W7" t="s">
+        <v>81</v>
+      </c>
+      <c r="X7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y7" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z7" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA7" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB7" s="22">
+        <f t="shared" ca="1" si="4"/>
+        <v>45842</v>
+      </c>
+      <c r="AC7" s="27">
+        <f t="shared" ca="1" si="5"/>
+        <v>45842</v>
+      </c>
+      <c r="AD7" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE7" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF7" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG7" s="30">
+        <f t="shared" ca="1" si="6"/>
+        <v>45842</v>
+      </c>
+      <c r="AH7" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI7" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ7" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK7" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL7" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM7" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="AN7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP7" s="33">
+        <v>40</v>
+      </c>
+      <c r="AQ7" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS7" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU7" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV7" s="36">
+        <v>251</v>
+      </c>
+      <c r="AW7" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX7" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY7" s="36">
+        <v>100000088</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA7" s="37">
+        <v>35591</v>
+      </c>
+      <c r="BB7" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE7" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG7" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH7" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI7" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ7" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK7" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL7" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM7">
+        <v>40</v>
+      </c>
+      <c r="BN7" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="41">
+        <v>10700444</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45842</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T8" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="W8" t="s">
+        <v>81</v>
+      </c>
+      <c r="X8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y8" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z8" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA8" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB8" s="22">
+        <f t="shared" ca="1" si="4"/>
+        <v>45842</v>
+      </c>
+      <c r="AC8" s="27">
+        <f t="shared" ca="1" si="5"/>
+        <v>45842</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE8" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF8" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG8" s="30">
+        <f t="shared" ca="1" si="6"/>
+        <v>45842</v>
+      </c>
+      <c r="AH8" s="22">
+        <v>44986</v>
+      </c>
+      <c r="AI8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ8" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK8" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL8" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="AM8" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN8" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO8" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP8" s="33">
+        <v>25</v>
+      </c>
+      <c r="AQ8" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS8" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU8" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW8" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX8" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY8" s="36">
+        <v>100000089</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA8" s="37">
+        <v>35709</v>
+      </c>
+      <c r="BB8" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE8" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>101</v>
+      </c>
+      <c r="BG8" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BH8" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI8" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ8" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BK8" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="BL8" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM8">
+        <v>38</v>
+      </c>
+      <c r="BN8" s="38" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA8" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2 V2:V3 S2:S3 K2:K3 BK2:BK3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2 V2:V8 S2:S8 K2:K8 BK2:BK8 AI8 AI6 AI4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT(#REF!)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="U3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="U5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="U6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="U7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="U8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
